--- a/CodeSystem-ACCESSEligibilityResultCS.xlsx
+++ b/CodeSystem-ACCESSEligibilityResultCS.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-26T23:16:42-05:00</t>
+    <t>2026-03-06T16:03:26-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-ACCESSEligibilityResultCS.xlsx
+++ b/CodeSystem-ACCESSEligibilityResultCS.xlsx
@@ -24,13 +24,13 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://globalalliantinc.com/access/CodeSystem/ACCESSEligibilityResultCS</t>
+    <t>https://dsacms.github.io/cmmi-access-model/CodeSystem/ACCESSEligibilityResultCS</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.9.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-06T16:03:26-05:00</t>
+    <t>2026-03-12T23:55:37-07:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-ACCESSEligibilityResultCS.xlsx
+++ b/CodeSystem-ACCESSEligibilityResultCS.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.1</t>
+    <t>0.9.6</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-12T23:55:37-07:00</t>
+    <t>2026-04-24T13:45:33-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-ACCESSEligibilityResultCS.xlsx
+++ b/CodeSystem-ACCESSEligibilityResultCS.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="73">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.6</t>
+    <t>0.9.8</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T13:45:33-04:00</t>
+    <t>2026-05-18T15:59:44-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -126,7 +126,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>8</t>
+    <t>10</t>
   </si>
   <si>
     <t>Level</t>
@@ -214,6 +214,24 @@
   </si>
   <si>
     <t>The patient is technically eligible, but is already aligned to another participant and receiving services under the ACCESS Model in the same track. A patient can only be aligned to one participant in each track.</t>
+  </si>
+  <si>
+    <t>not-eligible-clinical-exclusion</t>
+  </si>
+  <si>
+    <t>Not eligible - clinical exclusion</t>
+  </si>
+  <si>
+    <t>The patient has a clinical exclusion that prevents them from receiving services under the ACCESS Model.</t>
+  </si>
+  <si>
+    <t>not-eligible-mismatch</t>
+  </si>
+  <si>
+    <t>Not eligible - mismatch</t>
+  </si>
+  <si>
+    <t>The patient information provided does not match the patient information on record.</t>
   </si>
 </sst>
 </file>
@@ -525,7 +543,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -654,6 +672,34 @@
         <v>66</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="C10" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="D10" t="s" s="2">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="C11" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="D11" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/CodeSystem-ACCESSEligibilityResultCS.xlsx
+++ b/CodeSystem-ACCESSEligibilityResultCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-18T15:59:44-04:00</t>
+    <t>2026-05-20T09:30:43-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-ACCESSEligibilityResultCS.xlsx
+++ b/CodeSystem-ACCESSEligibilityResultCS.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.8</t>
+    <t>0.9.11</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-20T09:30:43-04:00</t>
+    <t>2026-06-04T22:54:52-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-ACCESSEligibilityResultCS.xlsx
+++ b/CodeSystem-ACCESSEligibilityResultCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-04T22:54:52-04:00</t>
+    <t>2026-06-04T23:05:21-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-ACCESSEligibilityResultCS.xlsx
+++ b/CodeSystem-ACCESSEligibilityResultCS.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.11</t>
+    <t>0.9.12</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-04T23:05:21-04:00</t>
+    <t>2026-06-10T23:08:55-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
